--- a/mapping/WorkForThursday.xlsx
+++ b/mapping/WorkForThursday.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dariushmokhlesi/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kianmokhlesi/Desktop/CLIF-OMOP-1/mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C58C958C-FA45-AF46-8AA0-E8710E5F7BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C93A4B-4AE7-2544-B1BA-EABEED7FC030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10460" yWindow="760" windowWidth="19780" windowHeight="17860" xr2:uid="{0387A755-F483-CE49-9D67-D0BEA0CB0C23}"/>
+    <workbookView xWindow="0" yWindow="700" windowWidth="27040" windowHeight="15420" xr2:uid="{0387A755-F483-CE49-9D67-D0BEA0CB0C23}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
